--- a/data/dividends_info_20260810.xlsx
+++ b/data/dividends_info_20260810.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>49.31000137329102</v>
+        <v>47.80500030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1825187537892645</v>
+        <v>0.1882648246531981</v>
       </c>
       <c r="J2" t="n">
         <v>217</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.65000152587891</v>
+        <v>67.09999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.050262541596797</v>
+        <v>1.043219099729151</v>
       </c>
       <c r="J3" t="n">
         <v>196</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.492000013589859</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.8130081076246635</v>
       </c>
       <c r="J5" t="n">
         <v>126</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>49.32500076293945</v>
+        <v>47.80500030517578</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1824632511057595</v>
+        <v>0.1882648246531981</v>
       </c>
       <c r="J6" t="n">
         <v>126</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.154999971389771</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="I7" t="n">
-        <v>3.573085894304783</v>
+        <v>3.58139518997746</v>
       </c>
       <c r="J7" t="n">
         <v>105</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.29500007629395</v>
+        <v>23.57500076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>1.159047001999216</v>
+        <v>1.145280980963731</v>
       </c>
       <c r="J8" t="n">
         <v>105</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22.97999954223633</v>
+        <v>23.29999923706055</v>
       </c>
       <c r="I9" t="n">
-        <v>2.567450007627734</v>
+        <v>2.532188924116173</v>
       </c>
       <c r="J9" t="n">
         <v>105</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.880000114440918</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I10" t="n">
-        <v>3.401360478017889</v>
+        <v>3.430531777311974</v>
       </c>
       <c r="J10" t="n">
         <v>98</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.60000038146973</v>
+        <v>10.90999984741211</v>
       </c>
       <c r="I11" t="n">
-        <v>4.339622485336358</v>
+        <v>4.216315366027376</v>
       </c>
       <c r="J11" t="n">
         <v>77</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I12" t="n">
-        <v>0.75</v>
+        <v>0.7894736941171157</v>
       </c>
       <c r="J12" t="n">
         <v>70</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.492000013589859</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.8130081076246635</v>
       </c>
       <c r="J13" t="n">
         <v>70</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.039999961853027</v>
+        <v>5.019999980926514</v>
       </c>
       <c r="I15" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7569721144298999</v>
       </c>
       <c r="J15" t="n">
         <v>49</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.29500007629395</v>
+        <v>23.57500076293945</v>
       </c>
       <c r="I16" t="n">
-        <v>1.159047001999216</v>
+        <v>1.145280980963731</v>
       </c>
       <c r="J16" t="n">
         <v>42</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.00600004196167</v>
+        <v>1.993000030517578</v>
       </c>
       <c r="I17" t="n">
-        <v>2.841475513841946</v>
+        <v>2.860009991329364</v>
       </c>
       <c r="J17" t="n">
         <v>42</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>49.32500076293945</v>
+        <v>47.80500030517578</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1824632511057595</v>
+        <v>0.1882648246531981</v>
       </c>
       <c r="J18" t="n">
         <v>42</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>99</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>1.343434343434344</v>
+        <v>1.355759450241843</v>
       </c>
       <c r="J19" t="n">
         <v>42</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.679999828338623</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I20" t="n">
-        <v>5.281690300468702</v>
+        <v>5.172413623006964</v>
       </c>
       <c r="J20" t="n">
         <v>35</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.492000013589859</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.8130081076246635</v>
       </c>
       <c r="J21" t="n">
         <v>14</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.900000095367432</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="I22" t="n">
-        <v>7.586206647076882</v>
+        <v>7.534246378487198</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.039999961853027</v>
+        <v>5.019999980926514</v>
       </c>
       <c r="I23" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7569721144298999</v>
       </c>
       <c r="J23" t="n">
         <v>-7</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.700000047683716</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="I25" t="n">
-        <v>5.480333236547166</v>
+        <v>5.583735648110744</v>
       </c>
       <c r="J25" t="n">
         <v>-7</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.800000190734863</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I26" t="n">
-        <v>4.310344685839137</v>
+        <v>4.237288067101817</v>
       </c>
       <c r="J26" t="n">
         <v>-14</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.968000411987305</v>
+        <v>9.937000274658203</v>
       </c>
       <c r="I28" t="n">
-        <v>2.608346601664759</v>
+        <v>2.616483775924451</v>
       </c>
       <c r="J28" t="n">
         <v>-21</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13.85999965667725</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="I29" t="n">
-        <v>4.329004436237065</v>
+        <v>4.360465043747729</v>
       </c>
       <c r="J29" t="n">
         <v>-21</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.680000066757202</v>
+        <v>2.657999992370605</v>
       </c>
       <c r="I30" t="n">
-        <v>8.20895501940042</v>
+        <v>8.276899948513067</v>
       </c>
       <c r="J30" t="n">
         <v>-21</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.492000013589859</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.8130081076246635</v>
       </c>
       <c r="J31" t="n">
         <v>-21</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.550000190734863</v>
+        <v>6.485000133514404</v>
       </c>
       <c r="I32" t="n">
-        <v>3.664122030705983</v>
+        <v>3.700848034831685</v>
       </c>
       <c r="J32" t="n">
         <v>-21</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>18.39999961853027</v>
+        <v>18.95000076293945</v>
       </c>
       <c r="I33" t="n">
-        <v>2.04347830323506</v>
+        <v>1.984168785551417</v>
       </c>
       <c r="J33" t="n">
         <v>-21</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.659999847412109</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="I35" t="n">
-        <v>2.120141399913057</v>
+        <v>2.123893769460125</v>
       </c>
       <c r="J35" t="n">
         <v>-28</v>
@@ -2779,95 +2779,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CELLULARLINE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CELLULARLINE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Esprinet S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OPS Italia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>